--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="474">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -821,6 +821,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7758,7 +7762,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>263</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7766,10 +7770,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7795,10 +7799,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7829,7 +7833,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7847,7 +7851,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7867,10 +7871,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7968,10 +7972,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8012,7 +8016,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -8071,10 +8075,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8174,10 +8178,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8277,10 +8281,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8380,10 +8384,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8483,10 +8487,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8584,10 +8588,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8685,10 +8689,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8788,10 +8792,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8891,10 +8895,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8994,10 +8998,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9020,13 +9024,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9077,7 +9081,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -9097,10 +9101,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9123,7 +9127,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -9156,7 +9160,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -9174,7 +9178,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9194,10 +9198,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9220,7 +9224,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -9273,7 +9277,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9293,10 +9297,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9352,25 +9356,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9390,10 +9394,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9419,10 +9423,10 @@
         <v>170</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9473,7 +9477,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9493,10 +9497,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9594,10 +9598,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9697,10 +9701,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9800,10 +9804,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9903,10 +9907,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10006,10 +10010,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10109,10 +10113,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10210,10 +10214,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10311,10 +10315,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10414,10 +10418,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10515,10 +10519,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10616,10 +10620,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10719,10 +10723,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10820,10 +10824,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10923,10 +10927,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11024,10 +11028,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11121,10 +11125,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11226,10 +11230,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11329,10 +11333,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11424,7 +11428,7 @@
         <v>74</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>74</v>
+        <v>263</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>74</v>
@@ -11432,10 +11436,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11535,10 +11539,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11638,10 +11642,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11664,13 +11668,13 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11701,7 +11705,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11719,7 +11723,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11739,10 +11743,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11765,7 +11769,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11798,25 +11802,25 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11836,10 +11840,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11866,7 +11870,7 @@
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11917,7 +11921,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11937,10 +11941,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11963,7 +11967,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -12016,7 +12020,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -12036,10 +12040,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12062,7 +12066,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -12115,7 +12119,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -12135,10 +12139,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12161,7 +12165,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12214,7 +12218,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -12234,10 +12238,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12260,7 +12264,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12313,7 +12317,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12333,10 +12337,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12359,7 +12363,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12412,7 +12416,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12432,10 +12436,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12458,7 +12462,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12511,7 +12515,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12531,10 +12535,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12557,7 +12561,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12598,7 +12602,7 @@
         <v>74</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AC106" s="2"/>
       <c r="AD106" t="s" s="2">
@@ -12608,7 +12612,7 @@
         <v>124</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12628,13 +12632,13 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>74</v>
@@ -12656,10 +12660,10 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -12711,7 +12715,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12731,10 +12735,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12832,10 +12836,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12933,10 +12937,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13034,10 +13038,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13135,10 +13139,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13238,10 +13242,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13341,10 +13345,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13444,10 +13448,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13547,10 +13551,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13648,10 +13652,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13688,7 +13692,7 @@
         <v>74</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>74</v>
@@ -13707,7 +13711,7 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>74</v>
@@ -13725,7 +13729,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>75</v>
@@ -13745,10 +13749,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13775,7 +13779,7 @@
       </c>
       <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13826,7 +13830,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13846,10 +13850,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13876,12 +13880,12 @@
       </c>
       <c r="L119" s="2"/>
       <c r="M119" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
@@ -13927,7 +13931,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13947,10 +13951,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14026,7 +14030,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14046,10 +14050,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14072,7 +14076,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14125,7 +14129,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14145,10 +14149,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14171,7 +14175,7 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -14224,7 +14228,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14244,10 +14248,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14270,7 +14274,7 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -14323,7 +14327,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14343,10 +14347,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14369,7 +14373,7 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -14422,7 +14426,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14442,10 +14446,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14468,7 +14472,7 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -14521,7 +14525,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14541,10 +14545,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14567,7 +14571,7 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -14620,7 +14624,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14640,10 +14644,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14666,7 +14670,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -14719,7 +14723,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14739,10 +14743,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14765,7 +14769,7 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -14818,7 +14822,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14838,10 +14842,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14864,7 +14868,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14917,7 +14921,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14937,10 +14941,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14963,7 +14967,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15016,7 +15020,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -15036,10 +15040,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15062,7 +15066,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15115,7 +15119,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15135,13 +15139,13 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>74</v>
@@ -15163,10 +15167,10 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
@@ -15218,7 +15222,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15238,10 +15242,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15339,10 +15343,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15440,10 +15444,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15541,10 +15545,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15642,10 +15646,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15745,10 +15749,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15848,10 +15852,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15951,10 +15955,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16054,10 +16058,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16155,10 +16159,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16195,7 +16199,7 @@
         <v>74</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>74</v>
@@ -16214,7 +16218,7 @@
       </c>
       <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>74</v>
@@ -16232,7 +16236,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>75</v>
@@ -16252,10 +16256,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16282,7 +16286,7 @@
       </c>
       <c r="L143" s="2"/>
       <c r="M143" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16294,7 +16298,7 @@
         <v>74</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>74</v>
@@ -16333,7 +16337,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16353,10 +16357,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16383,12 +16387,12 @@
       </c>
       <c r="L144" s="2"/>
       <c r="M144" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
@@ -16434,7 +16438,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16454,10 +16458,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16533,7 +16537,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16553,10 +16557,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16579,7 +16583,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16632,7 +16636,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -16652,10 +16656,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16678,7 +16682,7 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -16731,7 +16735,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16751,10 +16755,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16777,7 +16781,7 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -16830,7 +16834,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -16850,10 +16854,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16876,7 +16880,7 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -16929,7 +16933,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -16949,10 +16953,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16975,7 +16979,7 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -17028,7 +17032,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -17048,10 +17052,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17074,7 +17078,7 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
@@ -17127,7 +17131,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17147,10 +17151,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17173,7 +17177,7 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -17226,7 +17230,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17246,10 +17250,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17272,7 +17276,7 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17325,7 +17329,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17345,10 +17349,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17371,7 +17375,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17424,7 +17428,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17444,10 +17448,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17470,7 +17474,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17523,7 +17527,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17543,10 +17547,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17569,7 +17573,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17622,7 +17626,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -17642,10 +17646,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17668,7 +17672,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17721,7 +17725,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -17741,10 +17745,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17767,7 +17771,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17820,7 +17824,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17840,10 +17844,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17866,7 +17870,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -17919,7 +17923,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -17939,10 +17943,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17965,11 +17969,11 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -18020,7 +18024,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18040,10 +18044,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18141,10 +18145,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18242,10 +18246,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18343,10 +18347,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18444,10 +18448,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18547,10 +18551,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18650,10 +18654,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18753,10 +18757,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18856,10 +18860,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18957,10 +18961,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18994,7 +18998,7 @@
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>74</v>
@@ -19016,7 +19020,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>74</v>
@@ -19034,7 +19038,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -19054,10 +19058,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19080,7 +19084,7 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -19133,7 +19137,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>
@@ -19153,10 +19157,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19179,7 +19183,7 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -19232,7 +19236,7 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
